--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1104-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1104-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B76CC4B7-B558-4F0F-9213-19F3F7781D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC70B181-87F3-48A6-934E-5FFFDA506612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{47E1EB75-FA50-4122-B1B2-69A98F3741BF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E8668AA2-11F1-47D4-ABFB-D55F12B2909C}"/>
   </bookViews>
   <sheets>
     <sheet name="1104-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1607,24 +1607,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008702D-47C6-464C-9C3A-61367BECBCC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A475AA28-FC62-4E54-91BF-B3C47AE9DA6A}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1657,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1694,7 +1693,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1746,7 +1745,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1814,7 +1813,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1886,7 +1885,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2030,7 +2029,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2174,7 +2173,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2318,7 +2317,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2678,7 +2677,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2010</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2009</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2008</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="41">
         <v>2007</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2006</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2005</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2004</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2002</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2001</v>
       </c>
@@ -3542,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2000</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>1999</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1998</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>1997</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1996</v>
       </c>
@@ -3902,7 +3901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43">
         <v>1995</v>
       </c>
@@ -3974,7 +3973,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="45"/>
       <c r="B35" s="46"/>
       <c r="C35" s="20" t="s">
@@ -4002,7 +4001,7 @@
       <c r="W35" s="52"/>
       <c r="X35" s="48"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>1994</v>
       </c>
@@ -4074,7 +4073,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
       <c r="B37" s="56"/>
       <c r="C37" s="22" t="s">
@@ -4102,7 +4101,7 @@
       <c r="W37" s="62"/>
       <c r="X37" s="58"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="43">
         <v>1993</v>
       </c>
@@ -4174,7 +4173,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="45"/>
       <c r="B39" s="46"/>
       <c r="C39" s="20" t="s">
@@ -4202,7 +4201,7 @@
       <c r="W39" s="52"/>
       <c r="X39" s="48"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>1992</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="55"/>
       <c r="B41" s="56"/>
       <c r="C41" s="22" t="s">
@@ -4302,7 +4301,7 @@
       <c r="W41" s="62"/>
       <c r="X41" s="58"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="43">
         <v>1991</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="45"/>
       <c r="B43" s="46"/>
       <c r="C43" s="20" t="s">
@@ -4402,7 +4401,7 @@
       <c r="W43" s="52"/>
       <c r="X43" s="48"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>1990</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="55"/>
       <c r="B45" s="56"/>
       <c r="C45" s="22" t="s">
@@ -4502,7 +4501,7 @@
       <c r="W45" s="62"/>
       <c r="X45" s="58"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="43">
         <v>1989</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="45"/>
       <c r="B47" s="46"/>
       <c r="C47" s="20" t="s">
@@ -4602,7 +4601,7 @@
       <c r="W47" s="52"/>
       <c r="X47" s="48"/>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1988</v>
       </c>
@@ -4674,7 +4673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>1987</v>
       </c>
@@ -4746,7 +4745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1986</v>
       </c>
@@ -4818,7 +4817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>1985</v>
       </c>
@@ -4890,7 +4889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>1984</v>
       </c>
@@ -4962,7 +4961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="41">
         <v>1983</v>
       </c>
@@ -5034,7 +5033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="39" t="s">
         <v>69</v>
       </c>
